--- a/data/outputs/2. City of York Council (Final).xlsx
+++ b/data/outputs/2. City of York Council (Final).xlsx
@@ -431,162 +431,162 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Risk ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Project Stage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Project Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Owner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mitigating Action</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (pre-mitigation)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Likelihood (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Impact (1-10) (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Priority (post-mitigation)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Date Added</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (pre-mitigation)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (1-10) (post-mitigation)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Priority (post-mitigation)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Failure to discharge planning and listed building conditions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Failure to discharge planning and listed building conditions.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Design team and contractor to collate initial pack of information for discharge of conditions</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Design team and contractor to collate initial pack of information for discharge of conditions.</t>
-        </is>
+      <c r="J2" t="n">
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>1</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>Planning conditions impact on budget</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Planning conditions may increase project budget during pre-construction.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Extent of conditions known and to be reviewed and managed</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>5</v>
@@ -596,52 +596,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Review and manage the extent of known planning conditions to control budget impact.</t>
-        </is>
+      <c r="J3" t="n">
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="L3" t="n">
-        <v>4</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>Electricity provider works delayed or non-conforming</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Electricity provider works are delayed or non-conforming, impacting the programme for the new supply.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Orders for the electrical services have been placed by CYC direct</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -655,52 +655,52 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>The Project Manager must monitor and expedite the placed orders with CYC to ensure compliance and adherence to the programme.</t>
-        </is>
+      <c r="J4" t="n">
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
         <v>2</v>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>Building Control Sign Off delay due to lack of resources</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Building Control sign-off is delayed due to a lack of resources, requiring a design revisit.</t>
+          <t>Construction / Commissioning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Continue liaison with the Building Control Officer</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -714,170 +714,170 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Continue and intensify liaison efforts with the Building Control Officer to expedite the process.</t>
-        </is>
+      <c r="J5" t="n">
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
         <v>2</v>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>Impact of boat companies (City Cruises)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Impact of boat companies (City Cruises) on delivery and site servicing strategy.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Legal agreements are in place</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Ensure legal agreements with boat companies are in place and actively monitored.</t>
-        </is>
+      <c r="J6" t="n">
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>Party wall negotiations &amp; construction access</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Party wall negotiations and construction access may face neighbor objections causing program delays.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Appoint party wall surveyor and progress discussions with neighbours</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Appoint a party wall surveyor and proactively engage neighbors to resolve access issues.</t>
-        </is>
+      <c r="J7" t="n">
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>Failure to secure market interest for restaurant tenant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Failure to secure market interest for restaurant tenant impacts long-term revenue and project costs.</t>
+          <t>Pre-Construction / Operation</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Early engagement of agent for potential lettings. Sufficient expressions of interest</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -891,52 +891,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Engage letting agent early to generate sufficient expressions of interest from potential tenants.</t>
-        </is>
+      <c r="J8" t="n">
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
         <v>6</v>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>Increased construction costs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Increased construction costs due to exchange rate fluctuations on materials and impacts from international markets following political decisions.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Tender prices received and under review - Risk shall remain prominent where budget costs / provisional sums are included</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -950,56 +950,56 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Review tender prices received and maintain vigilance where budget costs or provisional sums are included.</t>
-        </is>
+      <c r="J9" t="n">
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
         <v>4</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R18</t>
+          <t>Sub-contractor insolvency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sub-contractor insolvency impacts the Main Contractor.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Construction Manager</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Contractor financial checks and vetting of subcontractors</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -1009,56 +1009,56 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Execute contractor financial checks and vetting of subcontractors.</t>
-        </is>
+      <c r="J10" t="n">
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" t="n">
-        <v>4</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>Surveys required to determine ground conditions/ contamination</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Surveys are required to determine ground conditions and potential contamination, which may necessitate design revisions or on-site remediation.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>GI survey undertaken, information obtained. Contamination results received. - Desk study provided by Arup</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>8</v>
@@ -1068,56 +1068,56 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Execute a GI survey, obtain and review the results, and incorporate findings from the provided desk study into the design.</t>
-        </is>
+      <c r="J11" t="n">
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
         <v>6</v>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>Identification of active movement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Identification of active ground movement that impacts project cost during remediation.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Ongoing monitoring by ARUP and monitoring specification included within contract documents</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>8</v>
@@ -1127,52 +1127,52 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Include ongoing monitoring specifications within the contract documents.</t>
-        </is>
+      <c r="J12" t="n">
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
         <v>6</v>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>Unidentified archaeology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unidentified archaeology requiring further evaluation with potential cost impact.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Environment Lead</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Evaluation of site undertaken</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1186,111 +1186,111 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>The Environmental Lead must execute a thorough evaluation of the site for archaeology.</t>
-        </is>
+      <c r="J13" t="n">
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
         <v>2</v>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>Additional surveys required</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional surveys are required, creating potential cost impacts.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Undertake outstanding surveys</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Undertake the outstanding surveys.</t>
-        </is>
+      <c r="J14" t="n">
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>Unrealistic programme submitted by contractor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The contractor has submitted an unrealistic programme.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Market tested</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1304,52 +1304,52 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Conduct market testing to validate the programme's realism and feasibility.</t>
-        </is>
+      <c r="J15" t="n">
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
         <v>4</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>Programme delays; due to flood levels impacting construction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Programme delays due to flood levels impacting construction.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Review historic flood data and issue to Contractor. Contingency plan to be developed</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1363,52 +1363,52 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Review historic flood data and issue to Contractor, and develop a contingency plan.</t>
-        </is>
+      <c r="J16" t="n">
+        <v>6</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
-      <c r="L16" t="n">
-        <v>6</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>Delay to design programme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Delay to design programme impacting client/contractor costs and schedule.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Implementation of IRS schedules design deliverables and clear responsibility for design</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1422,52 +1422,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Implement IRS schedules for design deliverables with clear responsibility assignments.</t>
-        </is>
+      <c r="J17" t="n">
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
         <v>4</v>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>Underpinning, piling and crack repairs to be considered</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Underpinning, piling and crack repairs may resolve existing structural issues but could cause new cracks elsewhere requiring additional repairs.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Detailed dilapidations surveys, crack monitors</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1481,111 +1481,111 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Conduct detailed dilapidations surveys and install crack monitors to assess structural movement.</t>
-        </is>
+      <c r="J18" t="n">
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" t="n">
         <v>6</v>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>Discovering structural unknowns</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Discovering structural unknowns during construction leads to costs for additional surveys and remediation works.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Undertake surveys early to determine unknowns. Allow suitable contingency for remediation. Biggest concerns being the tower underpinning and South Range</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Undertake surveys early to determine unknowns and allow suitable contingency for remediation.</t>
-        </is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="L19" t="n">
-        <v>5</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R35</t>
+          <t>Undetected services not identified on surveys and drawings</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Undetected services not identified on surveys and drawings causing programme delays, re-design needs, and cost impacts.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Utilities surveys maps obtained and plotted on SGA drawings. Careful excavation / groundworks when on site</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1599,115 +1599,115 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Obtain utilities survey maps, plot them on SGA drawings, and implement careful excavation/groundworks procedures on site.</t>
-        </is>
+      <c r="J20" t="n">
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
         <v>4</v>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>River source heat pump license approval by the Environment Agency; Refused</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Risk of delay due to Environment Agency refusal of the river source heat pump license approval.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Environment Lead</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Provisional consent obtained; continued dialogue required</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Maintain continued dialogue with the Environment Agency to secure final approval.</t>
-        </is>
+      <c r="J21" t="n">
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>Sourcing stone for remediation works</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The quarry supplying the required stone is closed, impacting the program and requiring new approvals for alternative stone.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Procurement Manager</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Investigate other quarries which supply the stone. Liaise with Historic England and the planning authority to have an alternative approved.</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>5</v>
@@ -1717,37 +1717,37 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Investigate alternative quarries and secure necessary approvals from Historic England and the planning authority for a substitute stone.</t>
-        </is>
+      <c r="J22" t="n">
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
       </c>
-      <c r="L22" t="n">
-        <v>4</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>Structural damage and the repairs required to the tower</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Structural damage to the tower requiring underpinning repairs during construction.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1757,71 +1757,71 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Post Contract</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Bullivants / Arup design and Vinci temporary works design to be reviewed in detail to mitigate any consequential delay. Building monitoring systems and locations to be agreed.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>Med</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Review Bullivants/Arup and Vinci temporary works designs in detail to mitigate delays and agree building monitoring systems.</t>
-        </is>
+      <c r="J23" t="n">
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
-      <c r="L23" t="n">
-        <v>5</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>Outstanding defects remaining unresolved</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Outstanding defects remain unresolved, leaving legacy issues and building defects that impact tenant occupation and satisfaction.</t>
+          <t>Commissioning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Decommissioning</t>
+          <t>Post Contract</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Post Contract</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Ability to resolve within the building contract. Use of retention</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1835,52 +1835,52 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Resolve defects within the building contract terms using retention mechanisms.</t>
-        </is>
+      <c r="J24" t="n">
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
         <v>4</v>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>Costs exceeds allocated budget (Non Construction costs)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Costs exceed allocated budget for non-construction items including consultant fees and furniture/fit-out works.</t>
+          <t>Construction / Commissioning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Review non construction costs prior to contract award and during construction</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1894,52 +1894,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Review non-construction costs prior to contract award and during construction phase.</t>
-        </is>
+      <c r="J25" t="n">
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
       </c>
-      <c r="L25" t="n">
-        <v>4</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R51</t>
+          <t>Incorrect estimation design errors and ambiguities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Incorrect estimation, design errors, and ambiguities lead to construction cost overruns.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Risk sits with CYC except CDP items</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1953,37 +1953,37 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>The Project Manager must ensure rigorous cost estimation reviews and clarify all design ambiguities before construction.</t>
-        </is>
+      <c r="J26" t="n">
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" t="n">
         <v>4</v>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R56</t>
+          <t>Availability of specialist labour / equipment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Availability of specialist labour and equipment may lead to changes in specification or the need to appoint specialists and commission bespoke works.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Post Contract</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Dialogue with main contractor &amp; supply chain</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2012,52 +2012,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Engage in dialogue with the main contractor and supply chain to secure resources.</t>
-        </is>
+      <c r="J27" t="n">
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" t="n">
         <v>4</v>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R61</t>
+          <t>Poor co-ordination with design team interfaces (contractor design portions)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poor coordination with design team interfaces for contractor design portions.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>CDP requirements have reduced from initial intent - Regular meetings to be held with Vinci and Design Team to discuss CDP interfaces.</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2071,96 +2071,96 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Hold regular meetings with Vinci and Design Team to discuss CDP interface requirements.</t>
-        </is>
+      <c r="J28" t="n">
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
         <v>4</v>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R62</t>
+          <t>Rights of Light</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rights of Light issues with adjoining owners during pre-construction phase.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Adjoining Owners</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Adjoining Owners</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Title report does not identify any issues</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Conduct thorough title reports to identify and address any Rights of Light issues before construction begins.</t>
-        </is>
+      <c r="J29" t="n">
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R64</t>
+          <t>Poor contractor performance during construction</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poor contractor performance during construction.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Post Contract</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Contract to be signed to protect client - performance bonds to be obtained</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2189,56 +2189,56 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Execute signed contracts with performance bonds to protect client interests and ensure contractor accountability.</t>
-        </is>
+      <c r="J30" t="n">
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
         <v>6</v>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R66</t>
+          <t>Unknown South Range structures</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Risk of discovering old basement structures causing issues with piling proposals.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Risk of discovering old basement causing issues with piling proposals</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>5</v>
@@ -2248,111 +2248,111 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Conduct a detailed pre-construction site investigation to identify and map any unknown subsurface structures.</t>
-        </is>
+      <c r="J31" t="n">
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>4</v>
       </c>
-      <c r="L31" t="n">
-        <v>4</v>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>67</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R67</t>
+          <t>Insufficient design detail from specialist CDP packages</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Insufficient design detail from specialist CDP packages impacts sign-off of planning conditions and listed building consents, particularly pre-commencement conditions.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Regular design reviews and interface management</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Conduct regular design reviews and implement interface management protocols.</t>
-        </is>
+      <c r="J32" t="n">
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R70</t>
+          <t>Satisfying EA requirements</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>An incident occurring which stops the work due to failure to satisfy EA requirements, leading to an EA Prohibition.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Environment Lead</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Waste management and compliance with the EA to ensure no environmental hazards</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2366,52 +2366,52 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Implement waste management and ensure compliance with the EA to prevent environmental hazards and work stoppages.</t>
-        </is>
+      <c r="J33" t="n">
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
         <v>6</v>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R72</t>
+          <t>Delay in design programme due to tenant/operator requirements</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Delay in design programme due to tenant/operator requirements changes impacting cost and schedule.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Recovery of cost / time included within the Agreements for Lease should late or significant changes be made</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2425,52 +2425,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Include recovery of cost and time provisions within Agreements for Lease to address late or significant changes.</t>
-        </is>
+      <c r="J34" t="n">
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" t="n">
         <v>4</v>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R73</t>
+          <t>Design changes (including client changes/ variations / EOT &amp; loss &amp; expense claims) and unforeseen items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Design changes and unforeseen items leading to construction cost overruns.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Traditional contract — risk with CYC; secure adequate contingency</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2484,37 +2484,37 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Secure adequate contingency and manage traditional contract terms to transfer risk appropriately.</t>
-        </is>
+      <c r="J35" t="n">
+        <v>6</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
       </c>
-      <c r="L35" t="n">
-        <v>6</v>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>75</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R75</t>
+          <t>Weather delays</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Weather delays causing programme delays due to wind, temperature, and rain conditions.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Post Contract</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Contractor to provide impact and allowances via contract</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2543,52 +2543,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Contractor to provide impact assessments and weather allowances via contract terms.</t>
-        </is>
+      <c r="J36" t="n">
+        <v>4</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
       </c>
-      <c r="L36" t="n">
-        <v>4</v>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R76</t>
+          <t>Underpinning/ crack repairs by third parties</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Underpinning and crack repairs by third parties may cause cracks to appear elsewhere, leading to remediation costs.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Detailed dilapidations surveys, crack monitors</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2602,52 +2602,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Conduct detailed dilapidations surveys and install crack monitors.</t>
-        </is>
+      <c r="J37" t="n">
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
         <v>6</v>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>77</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R77</t>
+          <t>Ground conditions - Borehole survey depth insufficient</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Insufficient borehole survey depth impacts piling designs, requiring alterations with time and cost implications.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Additional bore hole surveys undertaken, no foundations / obstructions found albeit at relatively shallow depth. (near tower) Bullivants / Arup to review surveys and confirm they are happy with findings. Vinci to design piling to new structures and confirm site information held is adequate.</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2661,52 +2661,52 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Review and confirm survey findings with consultants, then design piling to new structures ensuring site information is adequate.</t>
-        </is>
+      <c r="J38" t="n">
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" t="n">
         <v>4</v>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R80</t>
+          <t>Instability to boundary wall following demolition</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Instability to boundary wall following demolition requiring structural works.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Assessment of wall structure required - Scope of works to be determined</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2720,52 +2720,52 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>The Lead engineer must execute an assessment of the wall structure to determine the required scope of works.</t>
-        </is>
+      <c r="J39" t="n">
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" t="n">
         <v>2</v>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R81</t>
+          <t>Clashes between the existing building foundations and proposed drainage network.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Clashes between existing building foundations and proposed drainage network due to lack of information about existing structures.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Trial holes could be undertaken to better understand the existing foundations.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2779,56 +2779,56 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Conduct trial holes to investigate existing foundations and maintain conservative drainage design with contingency allowances.</t>
-        </is>
+      <c r="J40" t="n">
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
-      </c>
-      <c r="L40" t="n">
         <v>2</v>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R82</t>
+          <t>Potential drainage clash with proposed lift shaft pits</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Potential drainage clash with proposed lift shaft pits requiring additional external drainage network.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Surveys</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Lead Engineer</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Trial hole dug in the location and appears to be clear - risk to be reviewed again once demolition of north annex is complete.</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>5</v>
@@ -2838,111 +2838,111 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Complete trial hole verification and review risk again after north annex demolition.</t>
-        </is>
+      <c r="J41" t="n">
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
         <v>4</v>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R83</t>
+          <t>Billing omissions or inaccuracies in BoQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Billing omissions or inaccuracies in the Bill of Quantities (BoQ) result in missing information, causing time and cost increases.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>T&amp;T have carried out reviews of the BoQ</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H42" t="n">
         <v>8</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>The Project Manager must ensure T&amp;T continues to carry out thorough reviews of the BoQ.</t>
-        </is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>4</v>
-      </c>
-      <c r="L42" t="n">
         <v>6</v>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R84</t>
+          <t>Additional works not covered by contract documents. Arising from opening up works / scope and extent of works greater than assumed etc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional works not covered by contract documents arise from opening up works or the scope and extent of works being greater than assumed, impacting cost and programme.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Detailed change management process to be followed.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2956,111 +2956,111 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Follow a detailed change management process.</t>
-        </is>
+      <c r="J43" t="n">
+        <v>6</v>
       </c>
       <c r="K43" t="n">
         <v>6</v>
       </c>
-      <c r="L43" t="n">
-        <v>6</v>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Med</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R85</t>
+          <t>Ongoing movement in the south range, given the removal of underpinning from the scheme</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ongoing movement in the south range due to removal of underpinning from the scheme, potentially requiring reinstatement with cost and time impacts.</t>
+          <t>Construction / Operation</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lead engineer</t>
+          <t>Monitoring during works</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Implement continuous monitoring during works to detect and respond to structural movement promptly.</t>
-        </is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>87</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R87</t>
+          <t>Design change due to level of development and coordination at the point of tender, for items such as North Annex chimney, retaining walls and stairs, and movement joints to existing structures</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Design changes due to insufficient development and coordination at tender stage for key structural elements may impact cost and schedule.</t>
+          <t>Pre-Construction</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pre-construction</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Coordination to be managed by design team as a priority - Design changes to retaining concrete wall has been instructed by CYC and should be underway by design team.</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3074,52 +3074,52 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Prioritize design team coordination and expedite instructed design changes for retaining walls and structural elements.</t>
-        </is>
+      <c r="J45" t="n">
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
         <v>2</v>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24-Mar-26</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R88</t>
+          <t>Council chamber cooling to be approved</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Council chamber cooling design requires approval, risking time and cost from revisiting proposals.</t>
+          <t>Commissioning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Decommissioning</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design Manager</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Design team to coordinate with planning / conservation</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3133,20 +3133,20 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Design team to coordinate with planning and conservation authorities for approval.</t>
-        </is>
+      <c r="J46" t="n">
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
         <v>4</v>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
